--- a/output/pdf_financials_xlsx/NSHS.xlsx
+++ b/output/pdf_financials_xlsx/NSHS.xlsx
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.272552</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.272552</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.272552</v>
       </c>
     </row>
     <row r="93">
@@ -2913,7 +2913,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -3132,7 +3136,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>1.272552</v>
       </c>

--- a/output/pdf_financials_xlsx/NSHS.xlsx
+++ b/output/pdf_financials_xlsx/NSHS.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.009316</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002022</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001886</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.009316</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002022</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001886</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.009316</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.002022</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
